--- a/base_clinicas.xlsx
+++ b/base_clinicas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFCE3EA4-EFB4-4A7B-9788-9842DDF7CC3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A16E9994-3E10-4CC3-B150-8917B435BA5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="0" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="REDES" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="776" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="800" uniqueCount="172">
   <si>
     <t>Aseguradora</t>
   </si>
@@ -56,9 +56,6 @@
     <t>Sin deducible al 80%</t>
   </si>
   <si>
-    <t>Santa Martha Del Sur, San Juan Bautista, Versalles, San Judas Tadeo, Centro Médico Medex</t>
-  </si>
-  <si>
     <t>Red 2</t>
   </si>
   <si>
@@ -68,9 +65,6 @@
     <t>1 día de cuarto al 80%</t>
   </si>
   <si>
-    <t>Bellavista, Cm Jockey Salud, Good Hope, Montefiori, Vesalio, Médica Cayetano Heredia, Medavan, Stella Maris, Aviva, Limatambo, Providencia</t>
-  </si>
-  <si>
     <t>Red 3</t>
   </si>
   <si>
@@ -80,9 +74,6 @@
     <t>1 día de cuarto al 75%</t>
   </si>
   <si>
-    <t>Centenario Peruano Japonesa, Javier Prado, San Gabriel, Tezza, Especialidades Médicas</t>
-  </si>
-  <si>
     <t>Red 4</t>
   </si>
   <si>
@@ -92,18 +83,12 @@
     <t>1 día de cuarto al 70%</t>
   </si>
   <si>
-    <t>Internacional  Lima, Jesús Del Norte</t>
-  </si>
-  <si>
     <t>Red 5</t>
   </si>
   <si>
     <t>S/95 al 60%</t>
   </si>
   <si>
-    <t>Internacional  San Borja, San Pablo</t>
-  </si>
-  <si>
     <t>Red Médica</t>
   </si>
   <si>
@@ -131,15 +116,9 @@
     <t>S/95 al 70%</t>
   </si>
   <si>
-    <t>Internacional  San Borja, Ricardo Palma, El Golf, Sanna San Borja, Santa Isabel, Hogar  San Juan De Dios, San Pablo</t>
-  </si>
-  <si>
     <t>Red 6</t>
   </si>
   <si>
-    <t>S/105 al 65%</t>
-  </si>
-  <si>
     <t>Angloamericana</t>
   </si>
   <si>
@@ -152,9 +131,6 @@
     <t>1 día de cuarto al 65%</t>
   </si>
   <si>
-    <t>Delgado, Montesur, San Felipe, Miraflores, Tezza</t>
-  </si>
-  <si>
     <t>Full Salud</t>
   </si>
   <si>
@@ -191,9 +167,6 @@
     <t>S/85 al 70%</t>
   </si>
   <si>
-    <t>S/90 al 65%</t>
-  </si>
-  <si>
     <t>S/100 al 60%</t>
   </si>
   <si>
@@ -515,9 +488,6 @@
     <t>Mapfre Independencia, Mapfre Magdalena, Mapfre San Miguel, Mapfre Surco</t>
   </si>
   <si>
-    <t>Montefiori, Providencia, Medavan, Médica Cayetano Heredia, San Judas Tadeo, Santa Martha Del Sur, Especialidades Médicas, Jesús Del Norte, Hogar  San Juan De Dios, San Juan Bautista</t>
-  </si>
-  <si>
     <t>Javier Prado, Cm Jockey Salud, Limatambo, San Gabriel, Good Hope, Vesalio, Tezza, Bellavista, Centenario Peruano Japonesa, Stella Maris, La Luz</t>
   </si>
   <si>
@@ -534,6 +504,39 @@
   </si>
   <si>
     <t>Santa Isabel, Internacional  San Borja, El Golf</t>
+  </si>
+  <si>
+    <t>Santa Martha Del Sur, San Judas Tadeo, Bellavista, Aviva</t>
+  </si>
+  <si>
+    <t>Limatambo, Providencia, Medavan, Stella Maris, Montefiori, Vesalio, Cm Jockey Salud, San Gabriel, Especialidades Médicas, Jesús Del Norte</t>
+  </si>
+  <si>
+    <t>Internacional Lima, Tezza, San Pablo</t>
+  </si>
+  <si>
+    <t>Internacional  San Borja</t>
+  </si>
+  <si>
+    <t>S/130 al 60%</t>
+  </si>
+  <si>
+    <t>Montesur, Sanna San Borja, Internacional  San Borja</t>
+  </si>
+  <si>
+    <t>Internacional Lima, Tezza, San Pablo, Ricardo Palma, El Golf, Santa Isabel, Hogar  San Juan De Dios</t>
+  </si>
+  <si>
+    <t>Angloamericana, San Felipe, Miraflores</t>
+  </si>
+  <si>
+    <t>San Juan Bautista, Centro Médico Medex, Integramédica</t>
+  </si>
+  <si>
+    <t>Centenario Peruano Japonesa, Javier Prado, Cayetano Heredia, Good Hope</t>
+  </si>
+  <si>
+    <t>Montefiori, Providencia, Medavan, Cayetano Heredia, San Judas Tadeo, Santa Martha Del Sur, Especialidades Médicas, Jesús Del Norte, Hogar  San Juan De Dios, San Juan Bautista</t>
   </si>
 </sst>
 </file>
@@ -896,8 +899,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F129"/>
+  <dimension ref="A1:F133"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.85546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -936,7 +945,7 @@
         <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>169</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -947,16 +956,16 @@
         <v>7</v>
       </c>
       <c r="C3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" t="s">
         <v>12</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>13</v>
       </c>
-      <c r="E3" t="s">
-        <v>14</v>
-      </c>
       <c r="F3" t="s">
-        <v>15</v>
+        <v>161</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -967,16 +976,16 @@
         <v>7</v>
       </c>
       <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" t="s">
         <v>16</v>
       </c>
-      <c r="D4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E4" t="s">
-        <v>18</v>
-      </c>
       <c r="F4" t="s">
-        <v>19</v>
+        <v>162</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -987,16 +996,16 @@
         <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D5" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E5" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F5" t="s">
-        <v>23</v>
+        <v>170</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -1007,16 +1016,16 @@
         <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D6" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E6" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F6" t="s">
-        <v>26</v>
+        <v>163</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -1024,19 +1033,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="C7" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="D7" t="s">
-        <v>28</v>
+        <v>109</v>
       </c>
       <c r="E7" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F7" t="s">
-        <v>11</v>
+        <v>164</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -1044,19 +1053,19 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C8" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D8" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="E8" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="F8" t="s">
-        <v>15</v>
+        <v>169</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -1064,19 +1073,19 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C9" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D9" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="E9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F9" t="s">
-        <v>19</v>
+        <v>161</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -1084,19 +1093,19 @@
         <v>6</v>
       </c>
       <c r="B10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" t="s">
         <v>27</v>
       </c>
-      <c r="C10" t="s">
-        <v>20</v>
-      </c>
-      <c r="D10" t="s">
-        <v>34</v>
-      </c>
       <c r="E10" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="F10" t="s">
-        <v>23</v>
+        <v>162</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -1104,19 +1113,19 @@
         <v>6</v>
       </c>
       <c r="B11" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C11" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="D11" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="E11" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="F11" t="s">
-        <v>36</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -1124,19 +1133,19 @@
         <v>6</v>
       </c>
       <c r="B12" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C12" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="D12" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="E12" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F12" t="s">
-        <v>39</v>
+        <v>167</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -1144,19 +1153,19 @@
         <v>6</v>
       </c>
       <c r="B13" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C13" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="D13" t="s">
-        <v>41</v>
+        <v>158</v>
       </c>
       <c r="E13" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="F13" t="s">
-        <v>43</v>
+        <v>166</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -1164,19 +1173,19 @@
         <v>6</v>
       </c>
       <c r="B14" t="s">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="C14" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="D14" t="s">
-        <v>45</v>
+        <v>109</v>
       </c>
       <c r="E14" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F14" t="s">
-        <v>11</v>
+        <v>168</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -1184,19 +1193,19 @@
         <v>6</v>
       </c>
       <c r="B15" t="s">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="C15" t="s">
-        <v>12</v>
+        <v>110</v>
       </c>
       <c r="D15" t="s">
-        <v>28</v>
+        <v>165</v>
       </c>
       <c r="E15" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F15" t="s">
-        <v>15</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -1204,19 +1213,19 @@
         <v>6</v>
       </c>
       <c r="B16" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="C16" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D16" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="E16" t="s">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="F16" t="s">
-        <v>19</v>
+        <v>169</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -1224,19 +1233,19 @@
         <v>6</v>
       </c>
       <c r="B17" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="C17" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="D17" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="E17" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F17" t="s">
-        <v>23</v>
+        <v>161</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -1244,19 +1253,19 @@
         <v>6</v>
       </c>
       <c r="B18" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="C18" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D18" t="s">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="E18" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F18" t="s">
-        <v>36</v>
+        <v>162</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -1264,19 +1273,19 @@
         <v>6</v>
       </c>
       <c r="B19" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="C19" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="D19" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="E19" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="F19" t="s">
-        <v>39</v>
+        <v>170</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -1284,19 +1293,19 @@
         <v>6</v>
       </c>
       <c r="B20" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="C20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" t="s">
         <v>40</v>
       </c>
-      <c r="D20" t="s">
-        <v>50</v>
-      </c>
       <c r="E20" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="F20" t="s">
-        <v>43</v>
+        <v>167</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -1304,19 +1313,19 @@
         <v>6</v>
       </c>
       <c r="B21" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="C21" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="D21" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E21" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="F21" t="s">
-        <v>11</v>
+        <v>166</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -1324,19 +1333,19 @@
         <v>6</v>
       </c>
       <c r="B22" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="C22" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="D22" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="E22" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="F22" t="s">
-        <v>15</v>
+        <v>168</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -1344,19 +1353,19 @@
         <v>6</v>
       </c>
       <c r="B23" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="C23" t="s">
+        <v>110</v>
+      </c>
+      <c r="D23" t="s">
+        <v>107</v>
+      </c>
+      <c r="E23" t="s">
         <v>16</v>
       </c>
-      <c r="D23" t="s">
-        <v>53</v>
-      </c>
-      <c r="E23" t="s">
-        <v>46</v>
-      </c>
       <c r="F23" t="s">
-        <v>19</v>
+        <v>112</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -1364,19 +1373,19 @@
         <v>6</v>
       </c>
       <c r="B24" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="C24" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D24" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="E24" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F24" t="s">
-        <v>23</v>
+        <v>169</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -1384,19 +1393,19 @@
         <v>6</v>
       </c>
       <c r="B25" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="C25" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D25" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="E25" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F25" t="s">
-        <v>36</v>
+        <v>161</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -1404,19 +1413,19 @@
         <v>6</v>
       </c>
       <c r="B26" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="C26" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="D26" t="s">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="E26" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="F26" t="s">
-        <v>39</v>
+        <v>162</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -1424,19 +1433,19 @@
         <v>6</v>
       </c>
       <c r="B27" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="C27" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="D27" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="E27" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="F27" t="s">
-        <v>43</v>
+        <v>170</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -1444,19 +1453,19 @@
         <v>6</v>
       </c>
       <c r="B28" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="C28" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="D28" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="E28" t="s">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="F28" t="s">
-        <v>61</v>
+        <v>167</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -1464,19 +1473,19 @@
         <v>6</v>
       </c>
       <c r="B29" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="C29" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="D29" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="E29" t="s">
-        <v>46</v>
+        <v>13</v>
       </c>
       <c r="F29" t="s">
-        <v>63</v>
+        <v>166</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -1484,19 +1493,19 @@
         <v>6</v>
       </c>
       <c r="B30" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="C30" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="D30" t="s">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="E30" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="F30" t="s">
-        <v>65</v>
+        <v>168</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -1504,19 +1513,19 @@
         <v>6</v>
       </c>
       <c r="B31" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="C31" t="s">
-        <v>20</v>
+        <v>110</v>
       </c>
       <c r="D31" t="s">
-        <v>66</v>
+        <v>107</v>
       </c>
       <c r="E31" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F31" t="s">
-        <v>67</v>
+        <v>112</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -1524,19 +1533,19 @@
         <v>6</v>
       </c>
       <c r="B32" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="C32" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="D32" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="E32" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="F32" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -1544,19 +1553,19 @@
         <v>6</v>
       </c>
       <c r="B33" t="s">
-        <v>70</v>
+        <v>49</v>
       </c>
       <c r="C33" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D33" t="s">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="E33" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="F33" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -1564,19 +1573,19 @@
         <v>6</v>
       </c>
       <c r="B34" t="s">
-        <v>70</v>
+        <v>49</v>
       </c>
       <c r="C34" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D34" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="E34" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F34" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -1584,19 +1593,19 @@
         <v>6</v>
       </c>
       <c r="B35" t="s">
-        <v>70</v>
+        <v>49</v>
       </c>
       <c r="C35" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D35" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="E35" t="s">
-        <v>46</v>
+        <v>13</v>
       </c>
       <c r="F35" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -1604,19 +1613,19 @@
         <v>6</v>
       </c>
       <c r="B36" t="s">
-        <v>70</v>
+        <v>49</v>
       </c>
       <c r="C36" t="s">
         <v>20</v>
       </c>
       <c r="D36" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="E36" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="F36" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -1624,19 +1633,19 @@
         <v>6</v>
       </c>
       <c r="B37" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="C37" t="s">
+        <v>8</v>
+      </c>
+      <c r="D37" t="s">
+        <v>23</v>
+      </c>
+      <c r="E37" t="s">
         <v>24</v>
       </c>
-      <c r="D37" t="s">
-        <v>73</v>
-      </c>
-      <c r="E37" t="s">
-        <v>14</v>
-      </c>
       <c r="F37" t="s">
-        <v>170</v>
+        <v>52</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -1644,19 +1653,19 @@
         <v>6</v>
       </c>
       <c r="B38" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="C38" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="D38" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="E38" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F38" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -1664,19 +1673,19 @@
         <v>6</v>
       </c>
       <c r="B39" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="C39" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D39" t="s">
-        <v>28</v>
+        <v>63</v>
       </c>
       <c r="E39" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="F39" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -1684,19 +1693,19 @@
         <v>6</v>
       </c>
       <c r="B40" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="C40" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D40" t="s">
-        <v>71</v>
+        <v>40</v>
       </c>
       <c r="E40" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F40" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -1704,19 +1713,19 @@
         <v>6</v>
       </c>
       <c r="B41" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="C41" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D41" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="E41" t="s">
-        <v>46</v>
+        <v>13</v>
       </c>
       <c r="F41" t="s">
-        <v>65</v>
+        <v>160</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -1724,19 +1733,19 @@
         <v>6</v>
       </c>
       <c r="B42" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="C42" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="D42" t="s">
-        <v>73</v>
+        <v>48</v>
       </c>
       <c r="E42" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F42" t="s">
-        <v>170</v>
+        <v>32</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -1744,1739 +1753,1819 @@
         <v>6</v>
       </c>
       <c r="B43" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="C43" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="D43" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
       <c r="E43" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F43" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>75</v>
+        <v>6</v>
       </c>
       <c r="B44" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="C44" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D44" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="E44" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F44" t="s">
-        <v>78</v>
+        <v>54</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>75</v>
+        <v>6</v>
       </c>
       <c r="B45" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="C45" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D45" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="E45" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="F45" t="s">
-        <v>80</v>
+        <v>56</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>75</v>
+        <v>6</v>
       </c>
       <c r="B46" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="C46" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D46" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E46" t="s">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="F46" t="s">
-        <v>81</v>
+        <v>160</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>75</v>
+        <v>6</v>
       </c>
       <c r="B47" t="s">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="C47" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="D47" t="s">
-        <v>83</v>
+        <v>48</v>
       </c>
       <c r="E47" t="s">
-        <v>46</v>
+        <v>16</v>
       </c>
       <c r="F47" t="s">
-        <v>78</v>
+        <v>32</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="B48" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="C48" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D48" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="E48" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="F48" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="B49" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="C49" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D49" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="E49" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F49" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="B50" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="C50" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D50" t="s">
-        <v>89</v>
+        <v>53</v>
       </c>
       <c r="E50" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F50" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="B51" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="C51" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D51" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="E51" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F51" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
+        <v>66</v>
+      </c>
+      <c r="B52" t="s">
+        <v>73</v>
+      </c>
+      <c r="C52" t="s">
+        <v>11</v>
+      </c>
+      <c r="D52" t="s">
         <v>75</v>
       </c>
-      <c r="B52" t="s">
-        <v>88</v>
-      </c>
-      <c r="C52" t="s">
+      <c r="E52" t="s">
         <v>16</v>
       </c>
-      <c r="D52" t="s">
-        <v>9</v>
-      </c>
-      <c r="E52" t="s">
-        <v>18</v>
-      </c>
       <c r="F52" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="B53" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="C53" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D53" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="E53" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="F53" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="B54" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="C54" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="D54" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="E54" t="s">
-        <v>94</v>
+        <v>26</v>
       </c>
       <c r="F54" t="s">
-        <v>95</v>
+        <v>69</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="B55" t="s">
-        <v>7</v>
+        <v>79</v>
       </c>
       <c r="C55" t="s">
-        <v>96</v>
+        <v>11</v>
       </c>
       <c r="D55" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
       <c r="E55" t="s">
-        <v>98</v>
+        <v>28</v>
       </c>
       <c r="F55" t="s">
-        <v>99</v>
+        <v>76</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="B56" t="s">
-        <v>7</v>
+        <v>79</v>
       </c>
       <c r="C56" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D56" t="s">
-        <v>100</v>
+        <v>9</v>
       </c>
       <c r="E56" t="s">
-        <v>101</v>
+        <v>16</v>
       </c>
       <c r="F56" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="B57" t="s">
-        <v>7</v>
+        <v>79</v>
       </c>
       <c r="C57" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D57" t="s">
-        <v>17</v>
+        <v>83</v>
       </c>
       <c r="E57" t="s">
-        <v>103</v>
+        <v>35</v>
       </c>
       <c r="F57" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="B58" t="s">
-        <v>7</v>
+        <v>79</v>
       </c>
       <c r="C58" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D58" t="s">
-        <v>105</v>
+        <v>64</v>
       </c>
       <c r="E58" t="s">
-        <v>106</v>
+        <v>85</v>
       </c>
       <c r="F58" t="s">
-        <v>107</v>
+        <v>86</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="B59" t="s">
         <v>7</v>
       </c>
       <c r="C59" t="s">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="D59" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="E59" t="s">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="F59" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="B60" t="s">
-        <v>110</v>
+        <v>7</v>
       </c>
       <c r="C60" t="s">
         <v>8</v>
       </c>
       <c r="D60" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="E60" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="F60" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="B61" t="s">
-        <v>110</v>
+        <v>7</v>
       </c>
       <c r="C61" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D61" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="E61" t="s">
-        <v>29</v>
+        <v>94</v>
       </c>
       <c r="F61" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="B62" t="s">
-        <v>110</v>
+        <v>7</v>
       </c>
       <c r="C62" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D62" t="s">
-        <v>32</v>
+        <v>96</v>
       </c>
       <c r="E62" t="s">
-        <v>33</v>
+        <v>97</v>
       </c>
       <c r="F62" t="s">
-        <v>112</v>
+        <v>98</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="B63" t="s">
-        <v>110</v>
+        <v>7</v>
       </c>
       <c r="C63" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D63" t="s">
-        <v>113</v>
+        <v>83</v>
       </c>
       <c r="E63" t="s">
-        <v>18</v>
+        <v>99</v>
       </c>
       <c r="F63" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="B64" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="C64" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="D64" t="s">
-        <v>35</v>
+        <v>88</v>
       </c>
       <c r="E64" t="s">
-        <v>18</v>
+        <v>89</v>
       </c>
       <c r="F64" t="s">
-        <v>115</v>
+        <v>90</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="B65" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="C65" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="D65" t="s">
-        <v>116</v>
+        <v>23</v>
       </c>
       <c r="E65" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F65" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="B66" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="C66" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="D66" t="s">
-        <v>118</v>
+        <v>27</v>
       </c>
       <c r="E66" t="s">
-        <v>94</v>
+        <v>28</v>
       </c>
       <c r="F66" t="s">
-        <v>39</v>
+        <v>103</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="C67" t="s">
-        <v>119</v>
+        <v>17</v>
       </c>
       <c r="D67" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="E67" t="s">
-        <v>94</v>
+        <v>16</v>
       </c>
       <c r="F67" t="s">
-        <v>121</v>
+        <v>105</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>122</v>
+        <v>101</v>
       </c>
       <c r="C68" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="D68" t="s">
-        <v>123</v>
+        <v>30</v>
       </c>
       <c r="E68" t="s">
-        <v>98</v>
+        <v>16</v>
       </c>
       <c r="F68" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="B69" t="s">
-        <v>122</v>
+        <v>101</v>
       </c>
       <c r="C69" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="D69" t="s">
-        <v>45</v>
+        <v>107</v>
       </c>
       <c r="E69" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="F69" t="s">
-        <v>124</v>
+        <v>108</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="B70" t="s">
-        <v>122</v>
+        <v>101</v>
       </c>
       <c r="C70" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="D70" t="s">
-        <v>52</v>
+        <v>109</v>
       </c>
       <c r="E70" t="s">
-        <v>46</v>
+        <v>85</v>
       </c>
       <c r="F70" t="s">
-        <v>125</v>
+        <v>32</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="B71" t="s">
-        <v>122</v>
+        <v>101</v>
       </c>
       <c r="C71" t="s">
-        <v>20</v>
+        <v>110</v>
       </c>
       <c r="D71" t="s">
-        <v>54</v>
+        <v>111</v>
       </c>
       <c r="E71" t="s">
-        <v>33</v>
+        <v>85</v>
       </c>
       <c r="F71" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="B72" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="C72" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="D72" t="s">
-        <v>34</v>
+        <v>114</v>
       </c>
       <c r="E72" t="s">
-        <v>14</v>
+        <v>89</v>
       </c>
       <c r="F72" t="s">
-        <v>115</v>
+        <v>90</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="B73" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="C73" t="s">
+        <v>11</v>
+      </c>
+      <c r="D73" t="s">
         <v>37</v>
       </c>
-      <c r="D73" t="s">
-        <v>25</v>
-      </c>
       <c r="E73" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F73" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="B74" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="C74" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="D74" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="E74" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="F74" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="B75" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="C75" t="s">
-        <v>119</v>
+        <v>17</v>
       </c>
       <c r="D75" t="s">
-        <v>128</v>
+        <v>46</v>
       </c>
       <c r="E75" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F75" t="s">
-        <v>121</v>
+        <v>105</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="B76" t="s">
-        <v>129</v>
+        <v>113</v>
       </c>
       <c r="C76" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="D76" t="s">
-        <v>123</v>
+        <v>29</v>
       </c>
       <c r="E76" t="s">
-        <v>98</v>
+        <v>13</v>
       </c>
       <c r="F76" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="B77" t="s">
-        <v>129</v>
+        <v>113</v>
       </c>
       <c r="C77" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="D77" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="E77" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="F77" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="B78" t="s">
-        <v>129</v>
+        <v>113</v>
       </c>
       <c r="C78" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="D78" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E78" t="s">
-        <v>46</v>
+        <v>13</v>
       </c>
       <c r="F78" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="B79" t="s">
-        <v>129</v>
+        <v>113</v>
       </c>
       <c r="C79" t="s">
-        <v>20</v>
+        <v>110</v>
       </c>
       <c r="D79" t="s">
-        <v>47</v>
+        <v>119</v>
       </c>
       <c r="E79" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="F79" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="B80" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="C80" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="D80" t="s">
-        <v>34</v>
+        <v>114</v>
       </c>
       <c r="E80" t="s">
-        <v>14</v>
+        <v>89</v>
       </c>
       <c r="F80" t="s">
-        <v>115</v>
+        <v>90</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="B81" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="C81" t="s">
+        <v>11</v>
+      </c>
+      <c r="D81" t="s">
         <v>37</v>
       </c>
-      <c r="D81" t="s">
-        <v>73</v>
-      </c>
       <c r="E81" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F81" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="B82" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="C82" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="D82" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E82" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="F82" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="B83" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="C83" t="s">
-        <v>119</v>
+        <v>17</v>
       </c>
       <c r="D83" t="s">
-        <v>116</v>
+        <v>39</v>
       </c>
       <c r="E83" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F83" t="s">
-        <v>121</v>
+        <v>105</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>130</v>
+        <v>66</v>
       </c>
       <c r="B84" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="C84" t="s">
-        <v>132</v>
+        <v>20</v>
       </c>
       <c r="D84" t="s">
-        <v>89</v>
+        <v>29</v>
       </c>
       <c r="E84" t="s">
-        <v>98</v>
+        <v>13</v>
       </c>
       <c r="F84" t="s">
-        <v>133</v>
+        <v>106</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>130</v>
+        <v>66</v>
       </c>
       <c r="B85" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="C85" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="D85" t="s">
-        <v>134</v>
+        <v>64</v>
       </c>
       <c r="E85" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="F85" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>130</v>
+        <v>66</v>
       </c>
       <c r="B86" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="C86" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="D86" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="E86" t="s">
-        <v>136</v>
+        <v>13</v>
       </c>
       <c r="F86" t="s">
-        <v>137</v>
+        <v>118</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>130</v>
+        <v>66</v>
       </c>
       <c r="B87" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="C87" t="s">
-        <v>16</v>
+        <v>110</v>
       </c>
       <c r="D87" t="s">
-        <v>55</v>
+        <v>107</v>
       </c>
       <c r="E87" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F87" t="s">
-        <v>138</v>
+        <v>112</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="B88" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="C88" t="s">
-        <v>20</v>
+        <v>123</v>
       </c>
       <c r="D88" t="s">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="E88" t="s">
-        <v>18</v>
+        <v>89</v>
       </c>
       <c r="F88" t="s">
-        <v>139</v>
+        <v>124</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="B89" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="C89" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="D89" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="E89" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="F89" t="s">
-        <v>141</v>
+        <v>126</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="B90" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="C90" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="D90" t="s">
-        <v>142</v>
+        <v>46</v>
       </c>
       <c r="E90" t="s">
-        <v>94</v>
+        <v>127</v>
       </c>
       <c r="F90" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="B91" t="s">
-        <v>144</v>
+        <v>122</v>
       </c>
       <c r="C91" t="s">
-        <v>132</v>
+        <v>14</v>
       </c>
       <c r="D91" t="s">
-        <v>89</v>
+        <v>47</v>
       </c>
       <c r="E91" t="s">
-        <v>98</v>
+        <v>13</v>
       </c>
       <c r="F91" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
+        <v>121</v>
+      </c>
+      <c r="B92" t="s">
+        <v>122</v>
+      </c>
+      <c r="C92" t="s">
+        <v>17</v>
+      </c>
+      <c r="D92" t="s">
+        <v>42</v>
+      </c>
+      <c r="E92" t="s">
+        <v>16</v>
+      </c>
+      <c r="F92" t="s">
         <v>130</v>
-      </c>
-      <c r="B92" t="s">
-        <v>144</v>
-      </c>
-      <c r="C92" t="s">
-        <v>8</v>
-      </c>
-      <c r="D92" t="s">
-        <v>86</v>
-      </c>
-      <c r="E92" t="s">
-        <v>18</v>
-      </c>
-      <c r="F92" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="B93" t="s">
-        <v>144</v>
+        <v>122</v>
       </c>
       <c r="C93" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D93" t="s">
-        <v>17</v>
+        <v>131</v>
       </c>
       <c r="E93" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="F93" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="B94" t="s">
-        <v>144</v>
+        <v>122</v>
       </c>
       <c r="C94" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="D94" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="E94" t="s">
-        <v>42</v>
+        <v>85</v>
       </c>
       <c r="F94" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="B95" t="s">
-        <v>149</v>
+        <v>135</v>
       </c>
       <c r="C95" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="D95" t="s">
+        <v>80</v>
+      </c>
+      <c r="E95" t="s">
         <v>89</v>
       </c>
-      <c r="E95" t="s">
-        <v>98</v>
-      </c>
       <c r="F95" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="B96" t="s">
-        <v>149</v>
+        <v>135</v>
       </c>
       <c r="C96" t="s">
         <v>8</v>
       </c>
       <c r="D96" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="E96" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F96" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="B97" t="s">
-        <v>149</v>
+        <v>135</v>
       </c>
       <c r="C97" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D97" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E97" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F97" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="B98" t="s">
-        <v>149</v>
+        <v>135</v>
       </c>
       <c r="C98" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D98" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="E98" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="F98" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="B99" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="C99" t="s">
-        <v>20</v>
+        <v>123</v>
       </c>
       <c r="D99" t="s">
-        <v>150</v>
+        <v>80</v>
       </c>
       <c r="E99" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="F99" t="s">
-        <v>151</v>
+        <v>124</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="B100" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="C100" t="s">
-        <v>132</v>
+        <v>8</v>
       </c>
       <c r="D100" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="E100" t="s">
-        <v>98</v>
+        <v>16</v>
       </c>
       <c r="F100" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="B101" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="C101" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D101" t="s">
-        <v>84</v>
+        <v>15</v>
       </c>
       <c r="E101" t="s">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="F101" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="B102" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="C102" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D102" t="s">
-        <v>9</v>
+        <v>138</v>
       </c>
       <c r="E102" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F102" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="B103" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="C103" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D103" t="s">
-        <v>17</v>
+        <v>141</v>
       </c>
       <c r="E103" t="s">
-        <v>14</v>
+        <v>85</v>
       </c>
       <c r="F103" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="B104" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="C104" t="s">
-        <v>20</v>
+        <v>123</v>
       </c>
       <c r="D104" t="s">
-        <v>147</v>
+        <v>80</v>
       </c>
       <c r="E104" t="s">
-        <v>22</v>
+        <v>89</v>
       </c>
       <c r="F104" t="s">
-        <v>151</v>
+        <v>124</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="B105" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="C105" t="s">
-        <v>132</v>
+        <v>8</v>
       </c>
       <c r="D105" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="E105" t="s">
-        <v>98</v>
+        <v>38</v>
       </c>
       <c r="F105" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="B106" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="C106" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D106" t="s">
+        <v>9</v>
+      </c>
+      <c r="E106" t="s">
         <v>28</v>
       </c>
-      <c r="E106" t="s">
-        <v>29</v>
-      </c>
       <c r="F106" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="B107" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="C107" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D107" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="E107" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="F107" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="B108" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="C108" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D108" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="E108" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="F108" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="B109" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="C109" t="s">
-        <v>20</v>
+        <v>123</v>
       </c>
       <c r="D109" t="s">
-        <v>34</v>
+        <v>80</v>
       </c>
       <c r="E109" t="s">
-        <v>14</v>
+        <v>89</v>
       </c>
       <c r="F109" t="s">
-        <v>151</v>
+        <v>124</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="B110" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="C110" t="s">
+        <v>8</v>
+      </c>
+      <c r="D110" t="s">
+        <v>23</v>
+      </c>
+      <c r="E110" t="s">
         <v>24</v>
       </c>
-      <c r="D110" t="s">
-        <v>154</v>
-      </c>
-      <c r="E110" t="s">
-        <v>22</v>
-      </c>
       <c r="F110" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="B111" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="C111" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="D111" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="E111" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="F111" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="B112" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="C112" t="s">
-        <v>132</v>
+        <v>14</v>
       </c>
       <c r="D112" t="s">
-        <v>89</v>
+        <v>125</v>
       </c>
       <c r="E112" t="s">
-        <v>98</v>
+        <v>28</v>
       </c>
       <c r="F112" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="B113" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="C113" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D113" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="E113" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="F113" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="B114" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="C114" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D114" t="s">
-        <v>28</v>
+        <v>145</v>
       </c>
       <c r="E114" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F114" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="B115" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="C115" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="D115" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E115" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="F115" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="B116" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="C116" t="s">
-        <v>20</v>
+        <v>123</v>
       </c>
       <c r="D116" t="s">
-        <v>54</v>
+        <v>80</v>
       </c>
       <c r="E116" t="s">
-        <v>33</v>
+        <v>89</v>
       </c>
       <c r="F116" t="s">
-        <v>151</v>
+        <v>124</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="B117" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="C117" t="s">
+        <v>8</v>
+      </c>
+      <c r="D117" t="s">
+        <v>37</v>
+      </c>
+      <c r="E117" t="s">
         <v>24</v>
       </c>
-      <c r="D117" t="s">
-        <v>55</v>
-      </c>
-      <c r="E117" t="s">
-        <v>14</v>
-      </c>
       <c r="F117" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="B118" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="C118" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="D118" t="s">
-        <v>73</v>
+        <v>23</v>
       </c>
       <c r="E118" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F118" t="s">
-        <v>157</v>
+        <v>137</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="B119" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="C119" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="D119" t="s">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E119" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="F119" t="s">
-        <v>158</v>
+        <v>139</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="B120" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="C120" t="s">
-        <v>119</v>
+        <v>17</v>
       </c>
       <c r="D120" t="s">
-        <v>116</v>
+        <v>46</v>
       </c>
       <c r="E120" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F120" t="s">
-        <v>126</v>
+        <v>142</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>159</v>
+        <v>121</v>
       </c>
       <c r="B121" t="s">
-        <v>160</v>
+        <v>147</v>
       </c>
       <c r="C121" t="s">
-        <v>161</v>
+        <v>20</v>
       </c>
       <c r="D121" t="s">
-        <v>162</v>
+        <v>47</v>
       </c>
       <c r="E121" t="s">
-        <v>98</v>
+        <v>13</v>
       </c>
       <c r="F121" t="s">
-        <v>163</v>
+        <v>132</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>159</v>
+        <v>121</v>
       </c>
       <c r="B122" t="s">
-        <v>160</v>
+        <v>147</v>
       </c>
       <c r="C122" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="D122" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="E122" t="s">
-        <v>46</v>
+        <v>13</v>
       </c>
       <c r="F122" t="s">
-        <v>164</v>
+        <v>148</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>159</v>
+        <v>121</v>
       </c>
       <c r="B123" t="s">
-        <v>160</v>
+        <v>147</v>
       </c>
       <c r="C123" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="D123" t="s">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="E123" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="F123" t="s">
-        <v>165</v>
+        <v>149</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>159</v>
+        <v>121</v>
       </c>
       <c r="B124" t="s">
-        <v>166</v>
+        <v>147</v>
       </c>
       <c r="C124" t="s">
-        <v>161</v>
+        <v>110</v>
       </c>
       <c r="D124" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="E124" t="s">
-        <v>98</v>
+        <v>19</v>
       </c>
       <c r="F124" t="s">
-        <v>163</v>
+        <v>117</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="B125" t="s">
-        <v>166</v>
+        <v>151</v>
       </c>
       <c r="C125" t="s">
-        <v>8</v>
+        <v>152</v>
       </c>
       <c r="D125" t="s">
-        <v>52</v>
+        <v>153</v>
       </c>
       <c r="E125" t="s">
-        <v>29</v>
+        <v>89</v>
       </c>
       <c r="F125" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="B126" t="s">
-        <v>166</v>
+        <v>151</v>
       </c>
       <c r="C126" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D126" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="E126" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="F126" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="B127" t="s">
-        <v>166</v>
+        <v>151</v>
       </c>
       <c r="C127" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D127" t="s">
-        <v>73</v>
+        <v>12</v>
       </c>
       <c r="E127" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="F127" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="B128" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="C128" t="s">
-        <v>20</v>
+        <v>152</v>
       </c>
       <c r="D128" t="s">
-        <v>168</v>
+        <v>80</v>
       </c>
       <c r="E128" t="s">
-        <v>18</v>
+        <v>89</v>
       </c>
       <c r="F128" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
+        <v>150</v>
+      </c>
+      <c r="B129" t="s">
+        <v>156</v>
+      </c>
+      <c r="C129" t="s">
+        <v>8</v>
+      </c>
+      <c r="D129" t="s">
+        <v>44</v>
+      </c>
+      <c r="E129" t="s">
+        <v>24</v>
+      </c>
+      <c r="F129" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>150</v>
+      </c>
+      <c r="B130" t="s">
+        <v>156</v>
+      </c>
+      <c r="C130" t="s">
+        <v>11</v>
+      </c>
+      <c r="D130" t="s">
+        <v>45</v>
+      </c>
+      <c r="E130" t="s">
+        <v>26</v>
+      </c>
+      <c r="F130" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>150</v>
+      </c>
+      <c r="B131" t="s">
+        <v>156</v>
+      </c>
+      <c r="C131" t="s">
+        <v>14</v>
+      </c>
+      <c r="D131" t="s">
+        <v>64</v>
+      </c>
+      <c r="E131" t="s">
+        <v>16</v>
+      </c>
+      <c r="F131" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>150</v>
+      </c>
+      <c r="B132" t="s">
+        <v>156</v>
+      </c>
+      <c r="C132" t="s">
+        <v>17</v>
+      </c>
+      <c r="D132" t="s">
+        <v>158</v>
+      </c>
+      <c r="E132" t="s">
+        <v>16</v>
+      </c>
+      <c r="F132" t="s">
         <v>159</v>
       </c>
-      <c r="B129" t="s">
-        <v>166</v>
-      </c>
-      <c r="C129" t="s">
-        <v>24</v>
-      </c>
-      <c r="D129" t="s">
-        <v>41</v>
-      </c>
-      <c r="E129" t="s">
-        <v>18</v>
-      </c>
-      <c r="F129" t="s">
-        <v>126</v>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>150</v>
+      </c>
+      <c r="B133" t="s">
+        <v>156</v>
+      </c>
+      <c r="C133" t="s">
+        <v>20</v>
+      </c>
+      <c r="D133" t="s">
+        <v>34</v>
+      </c>
+      <c r="E133" t="s">
+        <v>16</v>
+      </c>
+      <c r="F133" t="s">
+        <v>117</v>
       </c>
     </row>
   </sheetData>

--- a/base_clinicas.xlsx
+++ b/base_clinicas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A16E9994-3E10-4CC3-B150-8917B435BA5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F80DCCA-A1BD-4893-A3BB-281EF4598F99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="REDES" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="800" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="806" uniqueCount="173">
   <si>
     <t>Aseguradora</t>
   </si>
@@ -401,78 +401,33 @@
     <t>S/60 al 80%</t>
   </si>
   <si>
-    <t>San Judas Tadeo, Stella Maris, Limatambo</t>
-  </si>
-  <si>
     <t>Sin deducible al 85%</t>
   </si>
   <si>
-    <t>Bellavista, Providencia, San Juan Bautista, Santa Martha Del Sur, Versalles, Hogar  San Juan De Dios, La Luz, Centenario Peruano Japonesa, Good Hope, Jesús Del Norte, San Gabriel</t>
-  </si>
-  <si>
-    <t>Tezza, Cm Jockey Salud, Javier Prado, Vesalio</t>
-  </si>
-  <si>
-    <t>El Golf, Maisón De Santé</t>
-  </si>
-  <si>
     <t>S/130 al 55%</t>
   </si>
   <si>
-    <t>San Pablo, Santa Isabel</t>
-  </si>
-  <si>
     <t>S/150 al 55%</t>
   </si>
   <si>
-    <t>Delgado, Ricardo Palma, Sanna San Borja</t>
-  </si>
-  <si>
     <t>Medisalud Lite</t>
   </si>
   <si>
-    <t>Bellavista, Providencia, San Juan Bautista, Santa Martha Del Sur, Versalles, Hogar  San Juan De Dios, La Luz, Montefiori</t>
-  </si>
-  <si>
-    <t>Centenario Peruano Japonesa, Good Hope, Jesús Del Norte, San Gabriel, San Judas Tadeo, Stella Maris, Medavan</t>
-  </si>
-  <si>
     <t>S/75 al 65%</t>
   </si>
   <si>
-    <t>Limatambo, Tezza, Cm Jockey Salud, Javier Prado, Vesalio</t>
-  </si>
-  <si>
     <t>Medisalud Base</t>
   </si>
   <si>
-    <t>S/80 al 65%</t>
-  </si>
-  <si>
-    <t>El Golf</t>
-  </si>
-  <si>
     <t>Medisalud</t>
   </si>
   <si>
     <t>Medisalud Plus</t>
   </si>
   <si>
-    <t>S/100 al 70%</t>
-  </si>
-  <si>
-    <t>Ricardo Palma, Delgado, Sanna San Borja</t>
-  </si>
-  <si>
     <t>Medisalud Premium</t>
   </si>
   <si>
-    <t>Ricardo Palma, Delgado</t>
-  </si>
-  <si>
-    <t>Montesur, Internacional  San Borja, Sanna San Borja</t>
-  </si>
-  <si>
     <t>Mapfre Seguros</t>
   </si>
   <si>
@@ -537,6 +492,54 @@
   </si>
   <si>
     <t>Montefiori, Providencia, Medavan, Cayetano Heredia, San Judas Tadeo, Santa Martha Del Sur, Especialidades Médicas, Jesús Del Norte, Hogar  San Juan De Dios, San Juan Bautista</t>
+  </si>
+  <si>
+    <t>Cubierto al 90%</t>
+  </si>
+  <si>
+    <t>Montefiori, Cayetano Heredia</t>
+  </si>
+  <si>
+    <t>Stella Maris, San Judas Tadeo, Bellavista,  San Juan Bautista, Santa Martha Del Sur, Versalles, Hogar  San Juan De Dios, La Luz</t>
+  </si>
+  <si>
+    <t>Tezza, Jesús Del Norte, San Gabriel, Maisón De Santé, Javier Prado</t>
+  </si>
+  <si>
+    <t>San Pablo, Ricardo Palma, Urozen</t>
+  </si>
+  <si>
+    <t>San Juan Bautista, Santa Martha Del Sur, Versalles, Hogar  San Juan De Dios, La Luz, Montefiori</t>
+  </si>
+  <si>
+    <t>Limatambo, Centenario Peruano Japonesa, Good Hope, Providencia, Cm Jockey Salud, Vesalio</t>
+  </si>
+  <si>
+    <t>Good Hope, Centenario Peruano Japonesa, Providencia, Limatambo, Cm Jockey Salud, Vesalio, Medavan</t>
+  </si>
+  <si>
+    <t>Medex, Bellavista, San Judas Tadeo, Stella Maris</t>
+  </si>
+  <si>
+    <t>S/60 al 70%</t>
+  </si>
+  <si>
+    <t>Medex, Bellavista, San Judas Tadeo, Stella Maris, Medavan</t>
+  </si>
+  <si>
+    <t>Good Hope, Centenario Peruano Japonesa, Providencia, Limatambo, Cm Jockey Salud, Vesalio</t>
+  </si>
+  <si>
+    <t>S/105 al 65%</t>
+  </si>
+  <si>
+    <t>El Golf, Santa Isabel, Alvarez, Auna Guardia Cvil</t>
+  </si>
+  <si>
+    <t>Angloamericana, San Felipe, Delgado, Internacional San Borja</t>
+  </si>
+  <si>
+    <t>Sanna San Borja, Montesur</t>
   </si>
 </sst>
 </file>
@@ -555,6 +558,7 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -899,7 +903,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F133"/>
+  <dimension ref="A1:F134"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.85546875" bestFit="1" customWidth="1"/>
@@ -945,7 +949,7 @@
         <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -965,7 +969,7 @@
         <v>13</v>
       </c>
       <c r="F3" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -985,7 +989,7 @@
         <v>16</v>
       </c>
       <c r="F4" t="s">
-        <v>162</v>
+        <v>147</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -1005,7 +1009,7 @@
         <v>19</v>
       </c>
       <c r="F5" t="s">
-        <v>170</v>
+        <v>155</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -1025,7 +1029,7 @@
         <v>19</v>
       </c>
       <c r="F6" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -1045,7 +1049,7 @@
         <v>35</v>
       </c>
       <c r="F7" t="s">
-        <v>164</v>
+        <v>149</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -1065,7 +1069,7 @@
         <v>24</v>
       </c>
       <c r="F8" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -1085,7 +1089,7 @@
         <v>26</v>
       </c>
       <c r="F9" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -1105,7 +1109,7 @@
         <v>28</v>
       </c>
       <c r="F10" t="s">
-        <v>162</v>
+        <v>147</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -1125,7 +1129,7 @@
         <v>13</v>
       </c>
       <c r="F11" t="s">
-        <v>170</v>
+        <v>155</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -1145,7 +1149,7 @@
         <v>16</v>
       </c>
       <c r="F12" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -1159,13 +1163,13 @@
         <v>31</v>
       </c>
       <c r="D13" t="s">
-        <v>158</v>
+        <v>143</v>
       </c>
       <c r="E13" t="s">
         <v>19</v>
       </c>
       <c r="F13" t="s">
-        <v>166</v>
+        <v>151</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -1185,7 +1189,7 @@
         <v>35</v>
       </c>
       <c r="F14" t="s">
-        <v>168</v>
+        <v>153</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -1199,7 +1203,7 @@
         <v>110</v>
       </c>
       <c r="D15" t="s">
-        <v>165</v>
+        <v>150</v>
       </c>
       <c r="E15" t="s">
         <v>35</v>
@@ -1225,7 +1229,7 @@
         <v>24</v>
       </c>
       <c r="F16" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -1245,7 +1249,7 @@
         <v>26</v>
       </c>
       <c r="F17" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -1265,7 +1269,7 @@
         <v>38</v>
       </c>
       <c r="F18" t="s">
-        <v>162</v>
+        <v>147</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -1285,7 +1289,7 @@
         <v>28</v>
       </c>
       <c r="F19" t="s">
-        <v>170</v>
+        <v>155</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -1305,7 +1309,7 @@
         <v>28</v>
       </c>
       <c r="F20" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -1325,7 +1329,7 @@
         <v>13</v>
       </c>
       <c r="F21" t="s">
-        <v>166</v>
+        <v>151</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -1345,7 +1349,7 @@
         <v>13</v>
       </c>
       <c r="F22" t="s">
-        <v>168</v>
+        <v>153</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -1385,7 +1389,7 @@
         <v>24</v>
       </c>
       <c r="F24" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -1405,7 +1409,7 @@
         <v>26</v>
       </c>
       <c r="F25" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -1425,7 +1429,7 @@
         <v>38</v>
       </c>
       <c r="F26" t="s">
-        <v>162</v>
+        <v>147</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -1445,7 +1449,7 @@
         <v>28</v>
       </c>
       <c r="F27" t="s">
-        <v>170</v>
+        <v>155</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -1465,7 +1469,7 @@
         <v>28</v>
       </c>
       <c r="F28" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -1485,7 +1489,7 @@
         <v>13</v>
       </c>
       <c r="F29" t="s">
-        <v>166</v>
+        <v>151</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -1505,7 +1509,7 @@
         <v>13</v>
       </c>
       <c r="F30" t="s">
-        <v>168</v>
+        <v>153</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -1725,7 +1729,7 @@
         <v>13</v>
       </c>
       <c r="F41" t="s">
-        <v>160</v>
+        <v>145</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -1825,7 +1829,7 @@
         <v>13</v>
       </c>
       <c r="F46" t="s">
-        <v>160</v>
+        <v>145</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -2659,7 +2663,7 @@
         <v>123</v>
       </c>
       <c r="D88" t="s">
-        <v>80</v>
+        <v>157</v>
       </c>
       <c r="E88" t="s">
         <v>89</v>
@@ -2685,7 +2689,7 @@
         <v>26</v>
       </c>
       <c r="F89" t="s">
-        <v>126</v>
+        <v>158</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
@@ -2702,10 +2706,10 @@
         <v>46</v>
       </c>
       <c r="E90" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F90" t="s">
-        <v>128</v>
+        <v>159</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
@@ -2725,7 +2729,7 @@
         <v>13</v>
       </c>
       <c r="F91" t="s">
-        <v>129</v>
+        <v>163</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
@@ -2745,7 +2749,7 @@
         <v>16</v>
       </c>
       <c r="F92" t="s">
-        <v>130</v>
+        <v>160</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
@@ -2759,13 +2763,13 @@
         <v>20</v>
       </c>
       <c r="D93" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E93" t="s">
         <v>35</v>
       </c>
       <c r="F93" t="s">
-        <v>132</v>
+        <v>170</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
@@ -2779,13 +2783,13 @@
         <v>31</v>
       </c>
       <c r="D94" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="E94" t="s">
         <v>85</v>
       </c>
       <c r="F94" t="s">
-        <v>134</v>
+        <v>161</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
@@ -2793,13 +2797,13 @@
         <v>121</v>
       </c>
       <c r="B95" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="C95" t="s">
         <v>123</v>
       </c>
       <c r="D95" t="s">
-        <v>80</v>
+        <v>157</v>
       </c>
       <c r="E95" t="s">
         <v>89</v>
@@ -2813,7 +2817,7 @@
         <v>121</v>
       </c>
       <c r="B96" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="C96" t="s">
         <v>8</v>
@@ -2825,7 +2829,7 @@
         <v>16</v>
       </c>
       <c r="F96" t="s">
-        <v>136</v>
+        <v>162</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -2833,7 +2837,7 @@
         <v>121</v>
       </c>
       <c r="B97" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="C97" t="s">
         <v>11</v>
@@ -2845,7 +2849,7 @@
         <v>19</v>
       </c>
       <c r="F97" t="s">
-        <v>137</v>
+        <v>165</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -2853,19 +2857,19 @@
         <v>121</v>
       </c>
       <c r="B98" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="C98" t="s">
         <v>14</v>
       </c>
       <c r="D98" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="E98" t="s">
         <v>35</v>
       </c>
       <c r="F98" t="s">
-        <v>139</v>
+        <v>164</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -2873,13 +2877,13 @@
         <v>121</v>
       </c>
       <c r="B99" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="C99" t="s">
         <v>123</v>
       </c>
       <c r="D99" t="s">
-        <v>80</v>
+        <v>157</v>
       </c>
       <c r="E99" t="s">
         <v>89</v>
@@ -2893,7 +2897,7 @@
         <v>121</v>
       </c>
       <c r="B100" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="C100" t="s">
         <v>8</v>
@@ -2902,10 +2906,10 @@
         <v>77</v>
       </c>
       <c r="E100" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="F100" t="s">
-        <v>136</v>
+        <v>162</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
@@ -2913,7 +2917,7 @@
         <v>121</v>
       </c>
       <c r="B101" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="C101" t="s">
         <v>11</v>
@@ -2922,10 +2926,10 @@
         <v>15</v>
       </c>
       <c r="E101" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F101" t="s">
-        <v>137</v>
+        <v>165</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
@@ -2933,19 +2937,19 @@
         <v>121</v>
       </c>
       <c r="B102" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="C102" t="s">
         <v>14</v>
       </c>
       <c r="D102" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="E102" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="F102" t="s">
-        <v>139</v>
+        <v>164</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
@@ -2953,19 +2957,19 @@
         <v>121</v>
       </c>
       <c r="B103" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="C103" t="s">
         <v>17</v>
       </c>
       <c r="D103" t="s">
-        <v>141</v>
+        <v>83</v>
       </c>
       <c r="E103" t="s">
-        <v>85</v>
+        <v>35</v>
       </c>
       <c r="F103" t="s">
-        <v>142</v>
+        <v>160</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
@@ -2973,13 +2977,13 @@
         <v>121</v>
       </c>
       <c r="B104" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="C104" t="s">
         <v>123</v>
       </c>
       <c r="D104" t="s">
-        <v>80</v>
+        <v>157</v>
       </c>
       <c r="E104" t="s">
         <v>89</v>
@@ -2993,19 +2997,19 @@
         <v>121</v>
       </c>
       <c r="B105" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="C105" t="s">
         <v>8</v>
       </c>
       <c r="D105" t="s">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="E105" t="s">
         <v>38</v>
       </c>
       <c r="F105" t="s">
-        <v>136</v>
+        <v>162</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
@@ -3013,19 +3017,19 @@
         <v>121</v>
       </c>
       <c r="B106" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="C106" t="s">
         <v>11</v>
       </c>
       <c r="D106" t="s">
-        <v>9</v>
+        <v>166</v>
       </c>
       <c r="E106" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="F106" t="s">
-        <v>137</v>
+        <v>167</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
@@ -3033,19 +3037,19 @@
         <v>121</v>
       </c>
       <c r="B107" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="C107" t="s">
         <v>14</v>
       </c>
       <c r="D107" t="s">
-        <v>15</v>
+        <v>96</v>
       </c>
       <c r="E107" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F107" t="s">
-        <v>139</v>
+        <v>168</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
@@ -3053,19 +3057,19 @@
         <v>121</v>
       </c>
       <c r="B108" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="C108" t="s">
         <v>17</v>
       </c>
       <c r="D108" t="s">
-        <v>138</v>
+        <v>18</v>
       </c>
       <c r="E108" t="s">
         <v>19</v>
       </c>
       <c r="F108" t="s">
-        <v>142</v>
+        <v>160</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
@@ -3073,13 +3077,13 @@
         <v>121</v>
       </c>
       <c r="B109" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="C109" t="s">
         <v>123</v>
       </c>
       <c r="D109" t="s">
-        <v>80</v>
+        <v>157</v>
       </c>
       <c r="E109" t="s">
         <v>89</v>
@@ -3093,7 +3097,7 @@
         <v>121</v>
       </c>
       <c r="B110" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="C110" t="s">
         <v>8</v>
@@ -3105,7 +3109,7 @@
         <v>24</v>
       </c>
       <c r="F110" t="s">
-        <v>136</v>
+        <v>162</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
@@ -3113,7 +3117,7 @@
         <v>121</v>
       </c>
       <c r="B111" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="C111" t="s">
         <v>11</v>
@@ -3125,7 +3129,7 @@
         <v>26</v>
       </c>
       <c r="F111" t="s">
-        <v>137</v>
+        <v>167</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
@@ -3133,19 +3137,19 @@
         <v>121</v>
       </c>
       <c r="B112" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="C112" t="s">
         <v>14</v>
       </c>
       <c r="D112" t="s">
-        <v>125</v>
+        <v>27</v>
       </c>
       <c r="E112" t="s">
         <v>28</v>
       </c>
       <c r="F112" t="s">
-        <v>139</v>
+        <v>168</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
@@ -3153,7 +3157,7 @@
         <v>121</v>
       </c>
       <c r="B113" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="C113" t="s">
         <v>17</v>
@@ -3165,7 +3169,7 @@
         <v>13</v>
       </c>
       <c r="F113" t="s">
-        <v>142</v>
+        <v>160</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
@@ -3173,19 +3177,19 @@
         <v>121</v>
       </c>
       <c r="B114" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="C114" t="s">
         <v>20</v>
       </c>
       <c r="D114" t="s">
-        <v>145</v>
+        <v>30</v>
       </c>
       <c r="E114" t="s">
         <v>19</v>
       </c>
       <c r="F114" t="s">
-        <v>132</v>
+        <v>170</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
@@ -3193,19 +3197,19 @@
         <v>121</v>
       </c>
       <c r="B115" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="C115" t="s">
         <v>31</v>
       </c>
       <c r="D115" t="s">
-        <v>34</v>
+        <v>169</v>
       </c>
       <c r="E115" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="F115" t="s">
-        <v>146</v>
+        <v>161</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
@@ -3213,19 +3217,19 @@
         <v>121</v>
       </c>
       <c r="B116" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="C116" t="s">
-        <v>123</v>
+        <v>33</v>
       </c>
       <c r="D116" t="s">
-        <v>80</v>
+        <v>109</v>
       </c>
       <c r="E116" t="s">
-        <v>89</v>
+        <v>35</v>
       </c>
       <c r="F116" t="s">
-        <v>124</v>
+        <v>172</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
@@ -3233,19 +3237,19 @@
         <v>121</v>
       </c>
       <c r="B117" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="C117" t="s">
-        <v>8</v>
+        <v>123</v>
       </c>
       <c r="D117" t="s">
-        <v>37</v>
+        <v>157</v>
       </c>
       <c r="E117" t="s">
-        <v>24</v>
+        <v>89</v>
       </c>
       <c r="F117" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
@@ -3253,19 +3257,19 @@
         <v>121</v>
       </c>
       <c r="B118" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="C118" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D118" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="E118" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F118" t="s">
-        <v>137</v>
+        <v>162</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
@@ -3273,19 +3277,19 @@
         <v>121</v>
       </c>
       <c r="B119" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="C119" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D119" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E119" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="F119" t="s">
-        <v>139</v>
+        <v>167</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
@@ -3293,19 +3297,19 @@
         <v>121</v>
       </c>
       <c r="B120" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="C120" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D120" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="E120" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="F120" t="s">
-        <v>142</v>
+        <v>168</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
@@ -3313,19 +3317,19 @@
         <v>121</v>
       </c>
       <c r="B121" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="C121" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D121" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="E121" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="F121" t="s">
-        <v>132</v>
+        <v>160</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
@@ -3333,19 +3337,19 @@
         <v>121</v>
       </c>
       <c r="B122" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="C122" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="D122" t="s">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="E122" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="F122" t="s">
-        <v>148</v>
+        <v>170</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
@@ -3353,19 +3357,19 @@
         <v>121</v>
       </c>
       <c r="B123" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="C123" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D123" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="E123" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F123" t="s">
-        <v>149</v>
+        <v>161</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
@@ -3373,198 +3377,218 @@
         <v>121</v>
       </c>
       <c r="B124" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="C124" t="s">
-        <v>110</v>
+        <v>33</v>
       </c>
       <c r="D124" t="s">
-        <v>107</v>
+        <v>42</v>
       </c>
       <c r="E124" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F124" t="s">
-        <v>117</v>
+        <v>172</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>150</v>
+        <v>121</v>
       </c>
       <c r="B125" t="s">
-        <v>151</v>
+        <v>134</v>
       </c>
       <c r="C125" t="s">
-        <v>152</v>
+        <v>110</v>
       </c>
       <c r="D125" t="s">
-        <v>153</v>
+        <v>107</v>
       </c>
       <c r="E125" t="s">
-        <v>89</v>
+        <v>19</v>
       </c>
       <c r="F125" t="s">
-        <v>154</v>
+        <v>171</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="B126" t="s">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="C126" t="s">
-        <v>8</v>
+        <v>137</v>
       </c>
       <c r="D126" t="s">
-        <v>45</v>
+        <v>138</v>
       </c>
       <c r="E126" t="s">
-        <v>38</v>
+        <v>89</v>
       </c>
       <c r="F126" t="s">
-        <v>171</v>
+        <v>139</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="B127" t="s">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="C127" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D127" t="s">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="E127" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="F127" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="B128" t="s">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="C128" t="s">
-        <v>152</v>
+        <v>11</v>
       </c>
       <c r="D128" t="s">
-        <v>80</v>
+        <v>12</v>
       </c>
       <c r="E128" t="s">
-        <v>89</v>
+        <v>28</v>
       </c>
       <c r="F128" t="s">
-        <v>154</v>
+        <v>140</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="B129" t="s">
-        <v>156</v>
+        <v>141</v>
       </c>
       <c r="C129" t="s">
-        <v>8</v>
+        <v>137</v>
       </c>
       <c r="D129" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="E129" t="s">
-        <v>24</v>
+        <v>89</v>
       </c>
       <c r="F129" t="s">
-        <v>171</v>
+        <v>139</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="B130" t="s">
+        <v>141</v>
+      </c>
+      <c r="C130" t="s">
+        <v>8</v>
+      </c>
+      <c r="D130" t="s">
+        <v>44</v>
+      </c>
+      <c r="E130" t="s">
+        <v>24</v>
+      </c>
+      <c r="F130" t="s">
         <v>156</v>
-      </c>
-      <c r="C130" t="s">
-        <v>11</v>
-      </c>
-      <c r="D130" t="s">
-        <v>45</v>
-      </c>
-      <c r="E130" t="s">
-        <v>26</v>
-      </c>
-      <c r="F130" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="B131" t="s">
-        <v>156</v>
+        <v>141</v>
       </c>
       <c r="C131" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D131" t="s">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="E131" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="F131" t="s">
-        <v>157</v>
+        <v>140</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="B132" t="s">
-        <v>156</v>
+        <v>141</v>
       </c>
       <c r="C132" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D132" t="s">
-        <v>158</v>
+        <v>64</v>
       </c>
       <c r="E132" t="s">
         <v>16</v>
       </c>
       <c r="F132" t="s">
-        <v>159</v>
+        <v>142</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="B133" t="s">
-        <v>156</v>
+        <v>141</v>
       </c>
       <c r="C133" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D133" t="s">
-        <v>34</v>
+        <v>143</v>
       </c>
       <c r="E133" t="s">
         <v>16</v>
       </c>
       <c r="F133" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>135</v>
+      </c>
+      <c r="B134" t="s">
+        <v>141</v>
+      </c>
+      <c r="C134" t="s">
+        <v>20</v>
+      </c>
+      <c r="D134" t="s">
+        <v>34</v>
+      </c>
+      <c r="E134" t="s">
+        <v>16</v>
+      </c>
+      <c r="F134" t="s">
         <v>117</v>
       </c>
     </row>

--- a/base_clinicas.xlsx
+++ b/base_clinicas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\actualizar tarifario\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F80DCCA-A1BD-4893-A3BB-281EF4598F99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81D44D94-8CF5-4648-9B15-246B9D18DA84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="REDES" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="806" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="806" uniqueCount="175">
   <si>
     <t>Aseguradora</t>
   </si>
@@ -536,10 +536,16 @@
     <t>El Golf, Santa Isabel, Alvarez, Auna Guardia Cvil</t>
   </si>
   <si>
-    <t>Angloamericana, San Felipe, Delgado, Internacional San Borja</t>
-  </si>
-  <si>
     <t>Sanna San Borja, Montesur</t>
+  </si>
+  <si>
+    <t>Santa Isabel, Ricardo Palma, Internacional San Borja</t>
+  </si>
+  <si>
+    <t>Sanna San Borja, Bellavista, Especialidades Médicas, El Golf, Maisón De Santé, Tezza, Internacional Lima, San Pablo</t>
+  </si>
+  <si>
+    <t>Angloamericana, San Felipe, Delgado, Internacional San Borja, Internacional Lima</t>
   </si>
 </sst>
 </file>
@@ -2569,7 +2575,7 @@
         <v>28</v>
       </c>
       <c r="F83" t="s">
-        <v>105</v>
+        <v>173</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
@@ -2589,7 +2595,7 @@
         <v>13</v>
       </c>
       <c r="F84" t="s">
-        <v>106</v>
+        <v>172</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
@@ -3229,7 +3235,7 @@
         <v>35</v>
       </c>
       <c r="F116" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
@@ -3389,7 +3395,7 @@
         <v>13</v>
       </c>
       <c r="F124" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
@@ -3409,7 +3415,7 @@
         <v>19</v>
       </c>
       <c r="F125" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">

--- a/base_clinicas.xlsx
+++ b/base_clinicas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\actualizar tarifario\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81D44D94-8CF5-4648-9B15-246B9D18DA84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0344EE8-046B-4096-B6A1-D6A87F94C499}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="806" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="806" uniqueCount="173">
   <si>
     <t>Aseguradora</t>
   </si>
@@ -203,9 +203,6 @@
     <t>S/95 al 55%</t>
   </si>
   <si>
-    <t>Santa Isabel, Internacional  San Borja</t>
-  </si>
-  <si>
     <t>Oro - Plan Red</t>
   </si>
   <si>
@@ -281,9 +278,6 @@
     <t>1 día de cuarto al 60%</t>
   </si>
   <si>
-    <t>Ricardo Palma, San Pablo, Internacional  San Borja</t>
-  </si>
-  <si>
     <t>Red Sanna - Centros Clínicos</t>
   </si>
   <si>
@@ -338,12 +332,6 @@
     <t>S/80 al 70%</t>
   </si>
   <si>
-    <t>Sanna San Borja, Bellavista, Especialidades Médicas, El Golf, Maisón De Santé, Tezza, Internacional  Lima, San Pablo</t>
-  </si>
-  <si>
-    <t>Santa Isabel, Ricardo Palma, Internacional  San Borja</t>
-  </si>
-  <si>
     <t>S/110 al 60%</t>
   </si>
   <si>
@@ -455,12 +443,6 @@
     <t>S/110 al 65%</t>
   </si>
   <si>
-    <t>Ricardo Palma, Sanna San Borja, Maisón De Santé, El Golf, Santa Isabel, Internacional  San Borja</t>
-  </si>
-  <si>
-    <t>Santa Isabel, Internacional  San Borja, El Golf</t>
-  </si>
-  <si>
     <t>Santa Martha Del Sur, San Judas Tadeo, Bellavista, Aviva</t>
   </si>
   <si>
@@ -470,15 +452,9 @@
     <t>Internacional Lima, Tezza, San Pablo</t>
   </si>
   <si>
-    <t>Internacional  San Borja</t>
-  </si>
-  <si>
     <t>S/130 al 60%</t>
   </si>
   <si>
-    <t>Montesur, Sanna San Borja, Internacional  San Borja</t>
-  </si>
-  <si>
     <t>Internacional Lima, Tezza, San Pablo, Ricardo Palma, El Golf, Santa Isabel, Hogar  San Juan De Dios</t>
   </si>
   <si>
@@ -546,6 +522,24 @@
   </si>
   <si>
     <t>Angloamericana, San Felipe, Delgado, Internacional San Borja, Internacional Lima</t>
+  </si>
+  <si>
+    <t>Internacional San Borja</t>
+  </si>
+  <si>
+    <t>Montesur, Sanna San Borja, Internacional San Borja</t>
+  </si>
+  <si>
+    <t>Santa Isabel, Internacional San Borja</t>
+  </si>
+  <si>
+    <t>Santa Isabel, Internacional San Borja, El Golf</t>
+  </si>
+  <si>
+    <t>Ricardo Palma, San Pablo, Internacional San Borja</t>
+  </si>
+  <si>
+    <t>Ricardo Palma, Sanna San Borja, Maisón De Santé, El Golf, Santa Isabel, Internacional San Borja, Internacional Lima</t>
   </si>
 </sst>
 </file>
@@ -955,7 +949,7 @@
         <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -975,7 +969,7 @@
         <v>13</v>
       </c>
       <c r="F3" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -995,7 +989,7 @@
         <v>16</v>
       </c>
       <c r="F4" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -1015,7 +1009,7 @@
         <v>19</v>
       </c>
       <c r="F5" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -1035,7 +1029,7 @@
         <v>19</v>
       </c>
       <c r="F6" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -1049,13 +1043,13 @@
         <v>31</v>
       </c>
       <c r="D7" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="E7" t="s">
         <v>35</v>
       </c>
       <c r="F7" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -1075,7 +1069,7 @@
         <v>24</v>
       </c>
       <c r="F8" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -1095,7 +1089,7 @@
         <v>26</v>
       </c>
       <c r="F9" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -1115,7 +1109,7 @@
         <v>28</v>
       </c>
       <c r="F10" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -1135,7 +1129,7 @@
         <v>13</v>
       </c>
       <c r="F11" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -1155,7 +1149,7 @@
         <v>16</v>
       </c>
       <c r="F12" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -1169,13 +1163,13 @@
         <v>31</v>
       </c>
       <c r="D13" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="E13" t="s">
         <v>19</v>
       </c>
       <c r="F13" t="s">
-        <v>151</v>
+        <v>168</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -1189,13 +1183,13 @@
         <v>33</v>
       </c>
       <c r="D14" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="E14" t="s">
         <v>35</v>
       </c>
       <c r="F14" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -1206,16 +1200,16 @@
         <v>22</v>
       </c>
       <c r="C15" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D15" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="E15" t="s">
         <v>35</v>
       </c>
       <c r="F15" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -1235,7 +1229,7 @@
         <v>24</v>
       </c>
       <c r="F16" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -1255,7 +1249,7 @@
         <v>26</v>
       </c>
       <c r="F17" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -1275,7 +1269,7 @@
         <v>38</v>
       </c>
       <c r="F18" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -1295,7 +1289,7 @@
         <v>28</v>
       </c>
       <c r="F19" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -1315,7 +1309,7 @@
         <v>28</v>
       </c>
       <c r="F20" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -1335,7 +1329,7 @@
         <v>13</v>
       </c>
       <c r="F21" t="s">
-        <v>151</v>
+        <v>168</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -1355,7 +1349,7 @@
         <v>13</v>
       </c>
       <c r="F22" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -1366,16 +1360,16 @@
         <v>36</v>
       </c>
       <c r="C23" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D23" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="E23" t="s">
         <v>16</v>
       </c>
       <c r="F23" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -1395,7 +1389,7 @@
         <v>24</v>
       </c>
       <c r="F24" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -1415,7 +1409,7 @@
         <v>26</v>
       </c>
       <c r="F25" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -1435,7 +1429,7 @@
         <v>38</v>
       </c>
       <c r="F26" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -1455,7 +1449,7 @@
         <v>28</v>
       </c>
       <c r="F27" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -1475,7 +1469,7 @@
         <v>28</v>
       </c>
       <c r="F28" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -1495,7 +1489,7 @@
         <v>13</v>
       </c>
       <c r="F29" t="s">
-        <v>151</v>
+        <v>168</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -1515,7 +1509,7 @@
         <v>13</v>
       </c>
       <c r="F30" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -1526,16 +1520,16 @@
         <v>43</v>
       </c>
       <c r="C31" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D31" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="E31" t="s">
         <v>16</v>
       </c>
       <c r="F31" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -1635,7 +1629,7 @@
         <v>16</v>
       </c>
       <c r="F36" t="s">
-        <v>60</v>
+        <v>169</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -1643,7 +1637,7 @@
         <v>6</v>
       </c>
       <c r="B37" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C37" t="s">
         <v>8</v>
@@ -1663,13 +1657,13 @@
         <v>6</v>
       </c>
       <c r="B38" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C38" t="s">
         <v>11</v>
       </c>
       <c r="D38" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E38" t="s">
         <v>26</v>
@@ -1683,13 +1677,13 @@
         <v>6</v>
       </c>
       <c r="B39" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C39" t="s">
         <v>14</v>
       </c>
       <c r="D39" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E39" t="s">
         <v>38</v>
@@ -1703,7 +1697,7 @@
         <v>6</v>
       </c>
       <c r="B40" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C40" t="s">
         <v>17</v>
@@ -1723,19 +1717,19 @@
         <v>6</v>
       </c>
       <c r="B41" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C41" t="s">
         <v>20</v>
       </c>
       <c r="D41" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E41" t="s">
         <v>13</v>
       </c>
       <c r="F41" t="s">
-        <v>145</v>
+        <v>170</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -1743,7 +1737,7 @@
         <v>6</v>
       </c>
       <c r="B42" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C42" t="s">
         <v>31</v>
@@ -1763,7 +1757,7 @@
         <v>6</v>
       </c>
       <c r="B43" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C43" t="s">
         <v>8</v>
@@ -1783,13 +1777,13 @@
         <v>6</v>
       </c>
       <c r="B44" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C44" t="s">
         <v>11</v>
       </c>
       <c r="D44" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E44" t="s">
         <v>26</v>
@@ -1803,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B45" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C45" t="s">
         <v>14</v>
       </c>
       <c r="D45" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E45" t="s">
         <v>38</v>
@@ -1823,19 +1817,19 @@
         <v>6</v>
       </c>
       <c r="B46" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C46" t="s">
         <v>20</v>
       </c>
       <c r="D46" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E46" t="s">
         <v>13</v>
       </c>
       <c r="F46" t="s">
-        <v>145</v>
+        <v>170</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -1843,7 +1837,7 @@
         <v>6</v>
       </c>
       <c r="B47" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C47" t="s">
         <v>31</v>
@@ -1860,50 +1854,50 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
+        <v>65</v>
+      </c>
+      <c r="B48" t="s">
         <v>66</v>
-      </c>
-      <c r="B48" t="s">
-        <v>67</v>
       </c>
       <c r="C48" t="s">
         <v>8</v>
       </c>
       <c r="D48" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E48" t="s">
         <v>13</v>
       </c>
       <c r="F48" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
+        <v>65</v>
+      </c>
+      <c r="B49" t="s">
         <v>66</v>
-      </c>
-      <c r="B49" t="s">
-        <v>67</v>
       </c>
       <c r="C49" t="s">
         <v>11</v>
       </c>
       <c r="D49" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E49" t="s">
         <v>19</v>
       </c>
       <c r="F49" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
+        <v>65</v>
+      </c>
+      <c r="B50" t="s">
         <v>66</v>
-      </c>
-      <c r="B50" t="s">
-        <v>67</v>
       </c>
       <c r="C50" t="s">
         <v>14</v>
@@ -1915,115 +1909,115 @@
         <v>35</v>
       </c>
       <c r="F50" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B51" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C51" t="s">
         <v>8</v>
       </c>
       <c r="D51" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E51" t="s">
         <v>38</v>
       </c>
       <c r="F51" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B52" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C52" t="s">
         <v>11</v>
       </c>
       <c r="D52" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E52" t="s">
         <v>16</v>
       </c>
       <c r="F52" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B53" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C53" t="s">
         <v>14</v>
       </c>
       <c r="D53" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E53" t="s">
         <v>19</v>
       </c>
       <c r="F53" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B54" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C54" t="s">
         <v>8</v>
       </c>
       <c r="D54" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E54" t="s">
         <v>26</v>
       </c>
       <c r="F54" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B55" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C55" t="s">
         <v>11</v>
       </c>
       <c r="D55" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E55" t="s">
         <v>28</v>
       </c>
       <c r="F55" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B56" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C56" t="s">
         <v>14</v>
@@ -2035,72 +2029,72 @@
         <v>16</v>
       </c>
       <c r="F56" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B57" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C57" t="s">
         <v>17</v>
       </c>
       <c r="D57" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E57" t="s">
         <v>35</v>
       </c>
       <c r="F57" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B58" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C58" t="s">
         <v>20</v>
       </c>
       <c r="D58" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E58" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F58" t="s">
-        <v>86</v>
+        <v>171</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B59" t="s">
         <v>7</v>
       </c>
       <c r="C59" t="s">
+        <v>85</v>
+      </c>
+      <c r="D59" t="s">
+        <v>86</v>
+      </c>
+      <c r="E59" t="s">
         <v>87</v>
       </c>
-      <c r="D59" t="s">
+      <c r="F59" t="s">
         <v>88</v>
-      </c>
-      <c r="E59" t="s">
-        <v>89</v>
-      </c>
-      <c r="F59" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B60" t="s">
         <v>7</v>
@@ -2109,18 +2103,18 @@
         <v>8</v>
       </c>
       <c r="D60" t="s">
+        <v>89</v>
+      </c>
+      <c r="E60" t="s">
+        <v>90</v>
+      </c>
+      <c r="F60" t="s">
         <v>91</v>
-      </c>
-      <c r="E60" t="s">
-        <v>92</v>
-      </c>
-      <c r="F60" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B61" t="s">
         <v>7</v>
@@ -2132,15 +2126,15 @@
         <v>15</v>
       </c>
       <c r="E61" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F61" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B62" t="s">
         <v>7</v>
@@ -2149,18 +2143,18 @@
         <v>14</v>
       </c>
       <c r="D62" t="s">
+        <v>94</v>
+      </c>
+      <c r="E62" t="s">
+        <v>95</v>
+      </c>
+      <c r="F62" t="s">
         <v>96</v>
-      </c>
-      <c r="E62" t="s">
-        <v>97</v>
-      </c>
-      <c r="F62" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B63" t="s">
         <v>7</v>
@@ -2169,41 +2163,41 @@
         <v>17</v>
       </c>
       <c r="D63" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E63" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F63" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B64" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C64" t="s">
         <v>8</v>
       </c>
       <c r="D64" t="s">
+        <v>86</v>
+      </c>
+      <c r="E64" t="s">
+        <v>87</v>
+      </c>
+      <c r="F64" t="s">
         <v>88</v>
-      </c>
-      <c r="E64" t="s">
-        <v>89</v>
-      </c>
-      <c r="F64" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B65" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C65" t="s">
         <v>11</v>
@@ -2215,15 +2209,15 @@
         <v>24</v>
       </c>
       <c r="F65" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C66" t="s">
         <v>14</v>
@@ -2235,35 +2229,35 @@
         <v>28</v>
       </c>
       <c r="F66" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C67" t="s">
         <v>17</v>
       </c>
       <c r="D67" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E67" t="s">
         <v>16</v>
       </c>
       <c r="F67" t="s">
-        <v>105</v>
+        <v>165</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B68" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C68" t="s">
         <v>20</v>
@@ -2275,44 +2269,44 @@
         <v>16</v>
       </c>
       <c r="F68" t="s">
-        <v>106</v>
+        <v>164</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B69" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C69" t="s">
         <v>31</v>
       </c>
       <c r="D69" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="E69" t="s">
         <v>19</v>
       </c>
       <c r="F69" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B70" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C70" t="s">
         <v>33</v>
       </c>
       <c r="D70" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="E70" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F70" t="s">
         <v>32</v>
@@ -2320,50 +2314,50 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B71" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C71" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D71" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E71" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F71" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B72" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C72" t="s">
         <v>8</v>
       </c>
       <c r="D72" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E72" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F72" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B73" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C73" t="s">
         <v>11</v>
@@ -2375,15 +2369,15 @@
         <v>24</v>
       </c>
       <c r="F73" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B74" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C74" t="s">
         <v>14</v>
@@ -2395,15 +2389,15 @@
         <v>38</v>
       </c>
       <c r="F74" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B75" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C75" t="s">
         <v>17</v>
@@ -2415,15 +2409,15 @@
         <v>28</v>
       </c>
       <c r="F75" t="s">
-        <v>105</v>
+        <v>165</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B76" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C76" t="s">
         <v>20</v>
@@ -2435,15 +2429,15 @@
         <v>13</v>
       </c>
       <c r="F76" t="s">
-        <v>106</v>
+        <v>164</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B77" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C77" t="s">
         <v>31</v>
@@ -2455,15 +2449,15 @@
         <v>13</v>
       </c>
       <c r="F77" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B78" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C78" t="s">
         <v>33</v>
@@ -2475,55 +2469,55 @@
         <v>13</v>
       </c>
       <c r="F78" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B79" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C79" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D79" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E79" t="s">
         <v>19</v>
       </c>
       <c r="F79" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B80" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C80" t="s">
         <v>8</v>
       </c>
       <c r="D80" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E80" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F80" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B81" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C81" t="s">
         <v>11</v>
@@ -2535,15 +2529,15 @@
         <v>24</v>
       </c>
       <c r="F81" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B82" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C82" t="s">
         <v>14</v>
@@ -2555,15 +2549,15 @@
         <v>38</v>
       </c>
       <c r="F82" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B83" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C83" t="s">
         <v>17</v>
@@ -2575,15 +2569,15 @@
         <v>28</v>
       </c>
       <c r="F83" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B84" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C84" t="s">
         <v>20</v>
@@ -2595,35 +2589,35 @@
         <v>13</v>
       </c>
       <c r="F84" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B85" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C85" t="s">
         <v>31</v>
       </c>
       <c r="D85" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E85" t="s">
         <v>13</v>
       </c>
       <c r="F85" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B86" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C86" t="s">
         <v>33</v>
@@ -2635,75 +2629,75 @@
         <v>13</v>
       </c>
       <c r="F86" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B87" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C87" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D87" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="E87" t="s">
         <v>19</v>
       </c>
       <c r="F87" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B88" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C88" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="D88" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="E88" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F88" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B89" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C89" t="s">
         <v>8</v>
       </c>
       <c r="D89" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="E89" t="s">
         <v>26</v>
       </c>
       <c r="F89" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B90" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C90" t="s">
         <v>11</v>
@@ -2712,18 +2706,18 @@
         <v>46</v>
       </c>
       <c r="E90" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="F90" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B91" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C91" t="s">
         <v>14</v>
@@ -2735,15 +2729,15 @@
         <v>13</v>
       </c>
       <c r="F91" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B92" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C92" t="s">
         <v>17</v>
@@ -2755,95 +2749,95 @@
         <v>16</v>
       </c>
       <c r="F92" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B93" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C93" t="s">
         <v>20</v>
       </c>
       <c r="D93" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E93" t="s">
         <v>35</v>
       </c>
       <c r="F93" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B94" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C94" t="s">
         <v>31</v>
       </c>
       <c r="D94" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="E94" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F94" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B95" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="C95" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="D95" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="E95" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F95" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B96" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="C96" t="s">
         <v>8</v>
       </c>
       <c r="D96" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E96" t="s">
         <v>16</v>
       </c>
       <c r="F96" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B97" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="C97" t="s">
         <v>11</v>
@@ -2855,75 +2849,75 @@
         <v>19</v>
       </c>
       <c r="F97" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B98" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="C98" t="s">
         <v>14</v>
       </c>
       <c r="D98" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E98" t="s">
         <v>35</v>
       </c>
       <c r="F98" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B99" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C99" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="D99" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="E99" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F99" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B100" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C100" t="s">
         <v>8</v>
       </c>
       <c r="D100" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E100" t="s">
         <v>38</v>
       </c>
       <c r="F100" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B101" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C101" t="s">
         <v>11</v>
@@ -2935,75 +2929,75 @@
         <v>16</v>
       </c>
       <c r="F101" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B102" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C102" t="s">
         <v>14</v>
       </c>
       <c r="D102" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E102" t="s">
         <v>19</v>
       </c>
       <c r="F102" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B103" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C103" t="s">
         <v>17</v>
       </c>
       <c r="D103" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E103" t="s">
         <v>35</v>
       </c>
       <c r="F103" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B104" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C104" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="D104" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="E104" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F104" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B105" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C105" t="s">
         <v>8</v>
@@ -3015,55 +3009,55 @@
         <v>38</v>
       </c>
       <c r="F105" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B106" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C106" t="s">
         <v>11</v>
       </c>
       <c r="D106" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="E106" t="s">
         <v>13</v>
       </c>
       <c r="F106" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B107" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C107" t="s">
         <v>14</v>
       </c>
       <c r="D107" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E107" t="s">
         <v>16</v>
       </c>
       <c r="F107" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B108" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C108" t="s">
         <v>17</v>
@@ -3075,35 +3069,35 @@
         <v>19</v>
       </c>
       <c r="F108" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B109" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C109" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="D109" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="E109" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F109" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B110" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C110" t="s">
         <v>8</v>
@@ -3115,15 +3109,15 @@
         <v>24</v>
       </c>
       <c r="F110" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B111" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C111" t="s">
         <v>11</v>
@@ -3135,15 +3129,15 @@
         <v>26</v>
       </c>
       <c r="F111" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B112" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C112" t="s">
         <v>14</v>
@@ -3155,15 +3149,15 @@
         <v>28</v>
       </c>
       <c r="F112" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B113" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C113" t="s">
         <v>17</v>
@@ -3175,15 +3169,15 @@
         <v>13</v>
       </c>
       <c r="F113" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B114" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C114" t="s">
         <v>20</v>
@@ -3195,75 +3189,75 @@
         <v>19</v>
       </c>
       <c r="F114" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B115" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C115" t="s">
         <v>31</v>
       </c>
       <c r="D115" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="E115" t="s">
         <v>19</v>
       </c>
       <c r="F115" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B116" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C116" t="s">
         <v>33</v>
       </c>
       <c r="D116" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="E116" t="s">
         <v>35</v>
       </c>
       <c r="F116" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B117" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C117" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="D117" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="E117" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F117" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B118" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C118" t="s">
         <v>8</v>
@@ -3275,15 +3269,15 @@
         <v>24</v>
       </c>
       <c r="F118" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B119" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C119" t="s">
         <v>11</v>
@@ -3295,15 +3289,15 @@
         <v>26</v>
       </c>
       <c r="F119" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B120" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C120" t="s">
         <v>14</v>
@@ -3315,15 +3309,15 @@
         <v>38</v>
       </c>
       <c r="F120" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B121" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C121" t="s">
         <v>17</v>
@@ -3335,15 +3329,15 @@
         <v>28</v>
       </c>
       <c r="F121" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B122" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C122" t="s">
         <v>20</v>
@@ -3355,15 +3349,15 @@
         <v>28</v>
       </c>
       <c r="F122" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B123" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C123" t="s">
         <v>31</v>
@@ -3375,15 +3369,15 @@
         <v>13</v>
       </c>
       <c r="F123" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B124" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C124" t="s">
         <v>33</v>
@@ -3395,55 +3389,55 @@
         <v>13</v>
       </c>
       <c r="F124" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B125" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C125" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D125" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="E125" t="s">
         <v>19</v>
       </c>
       <c r="F125" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
+        <v>131</v>
+      </c>
+      <c r="B126" t="s">
+        <v>132</v>
+      </c>
+      <c r="C126" t="s">
+        <v>133</v>
+      </c>
+      <c r="D126" t="s">
+        <v>134</v>
+      </c>
+      <c r="E126" t="s">
+        <v>87</v>
+      </c>
+      <c r="F126" t="s">
         <v>135</v>
-      </c>
-      <c r="B126" t="s">
-        <v>136</v>
-      </c>
-      <c r="C126" t="s">
-        <v>137</v>
-      </c>
-      <c r="D126" t="s">
-        <v>138</v>
-      </c>
-      <c r="E126" t="s">
-        <v>89</v>
-      </c>
-      <c r="F126" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B127" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="C127" t="s">
         <v>8</v>
@@ -3455,15 +3449,15 @@
         <v>38</v>
       </c>
       <c r="F127" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B128" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="C128" t="s">
         <v>11</v>
@@ -3475,35 +3469,35 @@
         <v>28</v>
       </c>
       <c r="F128" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
+        <v>131</v>
+      </c>
+      <c r="B129" t="s">
+        <v>137</v>
+      </c>
+      <c r="C129" t="s">
+        <v>133</v>
+      </c>
+      <c r="D129" t="s">
+        <v>79</v>
+      </c>
+      <c r="E129" t="s">
+        <v>87</v>
+      </c>
+      <c r="F129" t="s">
         <v>135</v>
-      </c>
-      <c r="B129" t="s">
-        <v>141</v>
-      </c>
-      <c r="C129" t="s">
-        <v>137</v>
-      </c>
-      <c r="D129" t="s">
-        <v>80</v>
-      </c>
-      <c r="E129" t="s">
-        <v>89</v>
-      </c>
-      <c r="F129" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B130" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C130" t="s">
         <v>8</v>
@@ -3515,15 +3509,15 @@
         <v>24</v>
       </c>
       <c r="F130" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B131" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C131" t="s">
         <v>11</v>
@@ -3535,55 +3529,55 @@
         <v>26</v>
       </c>
       <c r="F131" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B132" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C132" t="s">
         <v>14</v>
       </c>
       <c r="D132" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E132" t="s">
         <v>16</v>
       </c>
       <c r="F132" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B133" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C133" t="s">
         <v>17</v>
       </c>
       <c r="D133" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="E133" t="s">
         <v>16</v>
       </c>
       <c r="F133" t="s">
-        <v>144</v>
+        <v>172</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B134" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C134" t="s">
         <v>20</v>
@@ -3595,7 +3589,7 @@
         <v>16</v>
       </c>
       <c r="F134" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>
